--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487730_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487730_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.0844</v>
+        <v>5.0298</v>
       </c>
       <c r="E2" t="n">
         <v>3.8878</v>
       </c>
       <c r="F2" t="n">
-        <v>1.1966</v>
+        <v>1.1421</v>
       </c>
       <c r="G2" t="n">
         <v>3.1282</v>
@@ -610,13 +610,13 @@
         <v>1.7463</v>
       </c>
       <c r="S2" t="n">
-        <v>1.092</v>
+        <v>1.0374</v>
       </c>
       <c r="T2" t="n">
         <v>0.4867</v>
       </c>
       <c r="U2" t="n">
-        <v>0.6052</v>
+        <v>0.5507</v>
       </c>
       <c r="V2" t="n">
         <v>0.2821</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.3566</v>
+        <v>3.474</v>
       </c>
       <c r="E3" t="n">
-        <v>5.1008</v>
+        <v>4.3</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.7442</v>
+        <v>-0.826</v>
       </c>
       <c r="G3" t="n">
         <v>3.978</v>
@@ -688,13 +688,13 @@
         <v>2.1344</v>
       </c>
       <c r="S3" t="n">
-        <v>2.4084</v>
+        <v>1.5259</v>
       </c>
       <c r="T3" t="n">
-        <v>1.8214</v>
+        <v>1.0206</v>
       </c>
       <c r="U3" t="n">
-        <v>0.5871</v>
+        <v>0.5053</v>
       </c>
       <c r="V3" t="n">
         <v>-1.8358</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.6069</v>
+        <v>2.4429</v>
       </c>
       <c r="E4" t="n">
-        <v>3.2377</v>
+        <v>2.537</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3692</v>
+        <v>-0.0941</v>
       </c>
       <c r="G4" t="n">
         <v>-1.0561</v>
@@ -766,13 +766,13 @@
         <v>1.3582</v>
       </c>
       <c r="S4" t="n">
-        <v>3.4989</v>
+        <v>2.3348</v>
       </c>
       <c r="T4" t="n">
-        <v>2.1242</v>
+        <v>1.4235</v>
       </c>
       <c r="U4" t="n">
-        <v>1.3746</v>
+        <v>0.9113</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.664</v>
+        <v>1.61</v>
       </c>
       <c r="E5" t="n">
-        <v>1.4094</v>
+        <v>1.7097</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2546</v>
+        <v>-0.0997</v>
       </c>
       <c r="G5" t="n">
         <v>0.7025</v>
@@ -844,13 +844,13 @@
         <v>1.5523</v>
       </c>
       <c r="S5" t="n">
-        <v>0.9033</v>
+        <v>0.8493000000000001</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.2412</v>
+        <v>0.0591</v>
       </c>
       <c r="U5" t="n">
-        <v>1.1445</v>
+        <v>0.7902</v>
       </c>
       <c r="V5" t="n">
         <v>-0.3299</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>F. DIAZ ZARZUELA</t>
+          <t>M. RODRIGUEZ MORENO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2587</v>
+        <v>-0.2519</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.5989</v>
+        <v>-0.04</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8575</v>
+        <v>-0.2119</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.6947</v>
+        <v>-0.3854</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.697</v>
+        <v>0.0206</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.9977</v>
+        <v>-0.406</v>
       </c>
       <c r="J6" t="n">
-        <v>-1.4429</v>
+        <v>0.0206</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.1895</v>
+        <v>0.0206</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.2535</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.2517</v>
+        <v>-0.406</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.5075</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>0.2558</v>
+        <v>-0.406</v>
       </c>
       <c r="P6" t="n">
-        <v>0.3881</v>
+        <v>0.194</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.1642</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.5523</v>
+        <v>0.194</v>
       </c>
       <c r="S6" t="n">
-        <v>2.1772</v>
+        <v>-0.0606</v>
       </c>
       <c r="T6" t="n">
-        <v>1.3963</v>
+        <v>-0.0606</v>
       </c>
       <c r="U6" t="n">
-        <v>0.7809</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.6119</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>0.6119</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.2239</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. RODRIGUEZ MORENO</t>
+          <t>F. DIAZ ZARZUELA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.2519</v>
+        <v>-0.6873</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.04</v>
+        <v>-1.2996</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.2119</v>
+        <v>0.6122</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.3854</v>
+        <v>-1.6947</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0206</v>
+        <v>-0.697</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.406</v>
+        <v>-0.9977</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0206</v>
+        <v>-1.4429</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0206</v>
+        <v>-0.1895</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>-1.2535</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.406</v>
+        <v>-0.2517</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>-0.5075</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.406</v>
+        <v>0.2558</v>
       </c>
       <c r="P7" t="n">
-        <v>0.194</v>
+        <v>0.3881</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-1.1642</v>
       </c>
       <c r="R7" t="n">
-        <v>0.194</v>
+        <v>1.5523</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.0606</v>
+        <v>1.2312</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.0606</v>
+        <v>0.6956</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>0.5356</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-0.6119</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>0.6119</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-1.2239</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.0291</v>
+        <v>-1.0018</v>
       </c>
       <c r="E8" t="n">
         <v>-0.6867</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.3424</v>
+        <v>-0.3151</v>
       </c>
       <c r="G8" t="n">
         <v>-0.8986</v>
@@ -1078,13 +1078,13 @@
         <v>0.194</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.0424</v>
+        <v>-0.0151</v>
       </c>
       <c r="T8" t="n">
         <v>-0.0606</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0182</v>
+        <v>0.0454</v>
       </c>
       <c r="V8" t="n">
         <v>-0.2821</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. ALMENARA SANABRIAS</t>
+          <t>J. BUSTOS NGUEMA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.2544</v>
+        <v>-1.249</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.6317</v>
+        <v>-0.0737</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.6226</v>
+        <v>-1.1752</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.528</v>
+        <v>-0.3157</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.4813</v>
+        <v>0.0091</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.0467</v>
+        <v>-0.3248</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.6205000000000001</v>
+        <v>0.1018</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.5849</v>
+        <v>0.0206</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.0356</v>
+        <v>0.08119999999999999</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.9075</v>
+        <v>-0.4175</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.8964</v>
+        <v>-0.0115</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.0111</v>
+        <v>-0.406</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>-0.194</v>
       </c>
       <c r="Q9" t="n">
         <v>-0.194</v>
       </c>
       <c r="R9" t="n">
-        <v>0.194</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>0.2736</v>
+        <v>0.1548</v>
       </c>
       <c r="T9" t="n">
-        <v>0.1828</v>
+        <v>0.0185</v>
       </c>
       <c r="U9" t="n">
-        <v>0.09080000000000001</v>
+        <v>0.1363</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>-0.894</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-0.894</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. BUSTOS NGUEMA</t>
+          <t>A. ALMENARA SANABRIAS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.531</v>
+        <v>-1.3183</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.2739</v>
+        <v>-0.8319</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.257</v>
+        <v>-0.4864</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.3157</v>
+        <v>-1.528</v>
       </c>
       <c r="H10" t="n">
-        <v>0.0091</v>
+        <v>-1.4813</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3248</v>
+        <v>-0.0467</v>
       </c>
       <c r="J10" t="n">
-        <v>0.1018</v>
+        <v>-0.6205000000000001</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0206</v>
+        <v>-0.5849</v>
       </c>
       <c r="L10" t="n">
-        <v>0.08119999999999999</v>
+        <v>-0.0356</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.4175</v>
+        <v>-0.9075</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.0115</v>
+        <v>-0.8964</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.406</v>
+        <v>-0.0111</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.194</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
         <v>-0.194</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>0.194</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.1272</v>
+        <v>0.2097</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1817</v>
+        <v>-0.0174</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0545</v>
+        <v>0.2271</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.894</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.894</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.2436</v>
+        <v>-1.425</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.452</v>
+        <v>-0.8514</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.7916</v>
+        <v>-0.5736</v>
       </c>
       <c r="G11" t="n">
         <v>-1.1558</v>
@@ -1312,13 +1312,13 @@
         <v>0.3881</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.3997</v>
+        <v>0.4189</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.5451</v>
+        <v>0.0555</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1454</v>
+        <v>0.3634</v>
       </c>
       <c r="V11" t="n">
         <v>0.2821</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.6217</v>
+        <v>-2.4305</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.857</v>
+        <v>-2.1563</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.7648</v>
+        <v>-0.2742</v>
       </c>
       <c r="G12" t="n">
         <v>-1.2993</v>
@@ -1390,13 +1390,13 @@
         <v>1.5523</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.3627</v>
+        <v>0.8285</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.4229</v>
+        <v>0.2778</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0601</v>
+        <v>0.5507</v>
       </c>
       <c r="V12" t="n">
         <v>-0.9896</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.703</v>
+        <v>-2.8572</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.458</v>
+        <v>0.1426</v>
       </c>
       <c r="F13" t="n">
-        <v>-3.245</v>
+        <v>-2.9997</v>
       </c>
       <c r="G13" t="n">
         <v>-1.2165</v>
@@ -1468,13 +1468,13 @@
         <v>0.7761</v>
       </c>
       <c r="S13" t="n">
-        <v>0.3463</v>
+        <v>1.1922</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.12</v>
+        <v>0.4806</v>
       </c>
       <c r="U13" t="n">
-        <v>0.4664</v>
+        <v>0.7117</v>
       </c>
       <c r="V13" t="n">
         <v>0.6597</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.335899999999998</v>
+        <v>1.3357</v>
       </c>
       <c r="E14" t="n">
-        <v>6.6375</v>
+        <v>6.637500000000001</v>
       </c>
       <c r="F14" t="n">
-        <v>-5.301600000000001</v>
+        <v>-5.3016</v>
       </c>
       <c r="G14" t="n">
         <v>-1.7414</v>
@@ -1525,7 +1525,7 @@
         <v>11.4273</v>
       </c>
       <c r="L14" t="n">
-        <v>2.8921</v>
+        <v>2.892100000000001</v>
       </c>
       <c r="M14" t="n">
         <v>-16.0607</v>
@@ -1546,13 +1546,13 @@
         <v>11.642</v>
       </c>
       <c r="S14" t="n">
-        <v>9.707099999999999</v>
+        <v>9.706999999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>4.379300000000001</v>
+        <v>4.3793</v>
       </c>
       <c r="U14" t="n">
-        <v>5.327700000000001</v>
+        <v>5.3277</v>
       </c>
       <c r="V14" t="n">
         <v>-3.7194</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.6752</v>
+        <v>4.5662</v>
       </c>
       <c r="E15" t="n">
         <v>4.3245</v>
       </c>
       <c r="F15" t="n">
-        <v>0.3507</v>
+        <v>0.2416</v>
       </c>
       <c r="G15" t="n">
         <v>4.7778</v>
@@ -1624,13 +1624,13 @@
         <v>1.3582</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.5101</v>
+        <v>-0.6191</v>
       </c>
       <c r="T15" t="n">
         <v>-0.5451</v>
       </c>
       <c r="U15" t="n">
-        <v>0.035</v>
+        <v>-0.074</v>
       </c>
       <c r="V15" t="n">
         <v>0.9896</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.7857</v>
+        <v>2.0855</v>
       </c>
       <c r="E16" t="n">
         <v>2.4486</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.6629</v>
+        <v>-0.3631</v>
       </c>
       <c r="G16" t="n">
         <v>1.7069</v>
@@ -1702,13 +1702,13 @@
         <v>1.3582</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.2795</v>
+        <v>-0.9797</v>
       </c>
       <c r="T16" t="n">
         <v>-0.5451</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.7344000000000001</v>
+        <v>-0.4346</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.9681</v>
+        <v>0.5132</v>
       </c>
       <c r="E17" t="n">
-        <v>2.7822</v>
+        <v>2.3818</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.8141</v>
+        <v>-1.8686</v>
       </c>
       <c r="G17" t="n">
         <v>0.8052</v>
@@ -1780,13 +1780,13 @@
         <v>1.7463</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.255</v>
+        <v>-0.7099</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.0595</v>
+        <v>-0.4599</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1956</v>
+        <v>-0.2501</v>
       </c>
       <c r="V17" t="n">
         <v>0.6119</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.7349</v>
+        <v>0.3717</v>
       </c>
       <c r="E18" t="n">
-        <v>0.2406</v>
+        <v>0.3407</v>
       </c>
       <c r="F18" t="n">
-        <v>0.4944</v>
+        <v>0.031</v>
       </c>
       <c r="G18" t="n">
         <v>-0.7392</v>
@@ -1858,13 +1858,13 @@
         <v>1.3582</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.4199</v>
+        <v>-0.7831</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.7268</v>
+        <v>-0.6267</v>
       </c>
       <c r="U18" t="n">
-        <v>0.3069</v>
+        <v>-0.1564</v>
       </c>
       <c r="V18" t="n">
         <v>1.506</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.2683</v>
+        <v>0.2956</v>
       </c>
       <c r="E19" t="n">
         <v>0.3227</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.0543</v>
+        <v>-0.0271</v>
       </c>
       <c r="G19" t="n">
         <v>-0.0319</v>
@@ -1936,13 +1936,13 @@
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>0.0182</v>
+        <v>0.0454</v>
       </c>
       <c r="T19" t="n">
         <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0182</v>
+        <v>0.0454</v>
       </c>
       <c r="V19" t="n">
         <v>0.2821</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.4957</v>
+        <v>-0.2048</v>
       </c>
       <c r="E20" t="n">
-        <v>0.8577</v>
+        <v>0.9578</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.3534</v>
+        <v>-1.1626</v>
       </c>
       <c r="G20" t="n">
         <v>0.6766</v>
@@ -2014,13 +2014,13 @@
         <v>1.9403</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.7649</v>
+        <v>-1.474</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.7268</v>
+        <v>-0.6267</v>
       </c>
       <c r="U20" t="n">
-        <v>-1.0381</v>
+        <v>-0.8473000000000001</v>
       </c>
       <c r="V20" t="n">
         <v>-0.3776</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.6881</v>
+        <v>-0.9339</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.3398</v>
+        <v>-0.6401</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.3482</v>
+        <v>-0.2937</v>
       </c>
       <c r="G21" t="n">
         <v>0.5685</v>
@@ -2092,13 +2092,13 @@
         <v>1.9403</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.9462</v>
+        <v>-1.1919</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.12</v>
+        <v>-0.4203</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.8260999999999999</v>
+        <v>-0.7716</v>
       </c>
       <c r="V21" t="n">
         <v>0.6597</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>P. FUENTE DIEZ</t>
+          <t>J. MARTINEZ SANTOS</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.9549</v>
+        <v>-0.9419</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.3606</v>
+        <v>-0.6111</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.5943000000000001</v>
+        <v>-0.3309</v>
       </c>
       <c r="G22" t="n">
-        <v>0.1801</v>
+        <v>-1.9142</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.3304</v>
+        <v>-1.2646</v>
       </c>
       <c r="I22" t="n">
-        <v>0.5105</v>
+        <v>-0.6495</v>
       </c>
       <c r="J22" t="n">
-        <v>0.6701</v>
+        <v>-0.8386</v>
       </c>
       <c r="K22" t="n">
-        <v>0.0206</v>
+        <v>0.3337</v>
       </c>
       <c r="L22" t="n">
-        <v>0.6495</v>
+        <v>-1.1723</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.49</v>
+        <v>-1.0756</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.351</v>
+        <v>-1.5983</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.139</v>
+        <v>0.5227000000000001</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.9702</v>
+        <v>1.1642</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.9702</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1.1642</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.2126</v>
+        <v>-0.8038999999999999</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.0606</v>
+        <v>-0.3844</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1521</v>
+        <v>-0.4194</v>
       </c>
       <c r="V22" t="n">
-        <v>0.0478</v>
+        <v>0.6119</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>0.6119</v>
       </c>
       <c r="X22" t="n">
-        <v>0.0478</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>J. MARTINEZ SANTOS</t>
+          <t>P. FUENTE DIEZ</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.9875</v>
+        <v>-1.0367</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.7112000000000001</v>
+        <v>-0.3606</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.2763</v>
+        <v>-0.6761</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.9142</v>
+        <v>0.1801</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.2646</v>
+        <v>-0.3304</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.6495</v>
+        <v>0.5105</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.8386</v>
+        <v>0.6701</v>
       </c>
       <c r="K23" t="n">
-        <v>0.3337</v>
+        <v>0.0206</v>
       </c>
       <c r="L23" t="n">
-        <v>-1.1723</v>
+        <v>0.6495</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.0756</v>
+        <v>-0.49</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.5983</v>
+        <v>-0.351</v>
       </c>
       <c r="O23" t="n">
-        <v>0.5227000000000001</v>
+        <v>-0.139</v>
       </c>
       <c r="P23" t="n">
-        <v>1.1642</v>
+        <v>-0.9702</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>-0.9702</v>
       </c>
       <c r="R23" t="n">
-        <v>1.1642</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.8495</v>
+        <v>-0.2944</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.4845</v>
+        <v>-0.0606</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.3649</v>
+        <v>-0.2338</v>
       </c>
       <c r="V23" t="n">
-        <v>0.6119</v>
+        <v>0.0478</v>
       </c>
       <c r="W23" t="n">
-        <v>0.6119</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>0.0478</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>M. HERMOSO ALCUBILLA</t>
+          <t>J. GARCIA-LARRACHE SEGURA</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2281,73 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.7104</v>
+        <v>-1.6361</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.4702</v>
+        <v>-0.5332</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.2402</v>
+        <v>-1.103</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.7792</v>
+        <v>-1.5478</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.4432</v>
+        <v>-0.5907</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.3359</v>
+        <v>-0.9571</v>
       </c>
       <c r="J24" t="n">
-        <v>0.4355</v>
+        <v>-0.1886</v>
       </c>
       <c r="K24" t="n">
-        <v>1.0216</v>
+        <v>-0.1936</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.5861</v>
+        <v>0.005</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.2146</v>
+        <v>-1.3592</v>
       </c>
       <c r="N24" t="n">
-        <v>-1.4649</v>
+        <v>-0.3971</v>
       </c>
       <c r="O24" t="n">
-        <v>0.2502</v>
+        <v>-0.9621</v>
       </c>
       <c r="P24" t="n">
-        <v>0.194</v>
+        <v>1.1642</v>
       </c>
       <c r="Q24" t="n">
-        <v>-0.9702</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
         <v>1.1642</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.7954</v>
+        <v>-0.9704</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.6057</v>
+        <v>-0.6267</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.1897</v>
+        <v>-0.3437</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.3299</v>
+        <v>-0.2821</v>
       </c>
       <c r="W24" t="n">
-        <v>-0.3299</v>
+        <v>0.2821</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>-0.5642</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>J. GARCIA-LARRACHE SEGURA</t>
+          <t>M. HERMOSO ALCUBILLA</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-2.0905</v>
+        <v>-1.9101</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.6333</v>
+        <v>-1.3701</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.4573</v>
+        <v>-0.54</v>
       </c>
       <c r="G25" t="n">
-        <v>-1.5478</v>
+        <v>-0.7792</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.5907</v>
+        <v>-0.4432</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.9571</v>
+        <v>-0.3359</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.1886</v>
+        <v>0.4355</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.1936</v>
+        <v>1.0216</v>
       </c>
       <c r="L25" t="n">
-        <v>0.005</v>
+        <v>-0.5861</v>
       </c>
       <c r="M25" t="n">
-        <v>-1.3592</v>
+        <v>-1.2146</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.3971</v>
+        <v>-1.4649</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.9621</v>
+        <v>0.2502</v>
       </c>
       <c r="P25" t="n">
-        <v>1.1642</v>
+        <v>0.194</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>-0.9702</v>
       </c>
       <c r="R25" t="n">
         <v>1.1642</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.4248</v>
+        <v>-0.9951</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.7268</v>
+        <v>-0.5056</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.6981000000000001</v>
+        <v>-0.4895</v>
       </c>
       <c r="V25" t="n">
-        <v>-0.2821</v>
+        <v>-0.3299</v>
       </c>
       <c r="W25" t="n">
-        <v>0.2821</v>
+        <v>-0.3299</v>
       </c>
       <c r="X25" t="n">
-        <v>-0.5642</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-2.8409</v>
+        <v>-2.5045</v>
       </c>
       <c r="E26" t="n">
-        <v>-2.1595</v>
+        <v>-1.9593</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.6814</v>
+        <v>-0.5452</v>
       </c>
       <c r="G26" t="n">
         <v>-1.9616</v>
@@ -2482,13 +2482,13 @@
         <v>1.3582</v>
       </c>
       <c r="S26" t="n">
-        <v>-1.2674</v>
+        <v>-0.9308999999999999</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.7268</v>
+        <v>-0.5266</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.5406</v>
+        <v>-0.4043</v>
       </c>
       <c r="V26" t="n">
         <v>0</v>
@@ -2518,25 +2518,25 @@
         <v>-1.3358</v>
       </c>
       <c r="E27" t="n">
-        <v>5.3017</v>
+        <v>5.301699999999999</v>
       </c>
       <c r="F27" t="n">
-        <v>-6.6373</v>
+        <v>-6.637700000000001</v>
       </c>
       <c r="G27" t="n">
-        <v>1.741199999999999</v>
+        <v>1.741200000000001</v>
       </c>
       <c r="H27" t="n">
         <v>-2.9577</v>
       </c>
       <c r="I27" t="n">
-        <v>4.699300000000001</v>
+        <v>4.6993</v>
       </c>
       <c r="J27" t="n">
         <v>16.0607</v>
       </c>
       <c r="K27" t="n">
-        <v>8.4694</v>
+        <v>8.469399999999998</v>
       </c>
       <c r="L27" t="n">
         <v>7.591400000000002</v>
@@ -2560,19 +2560,19 @@
         <v>14.5523</v>
       </c>
       <c r="S27" t="n">
-        <v>-9.707100000000001</v>
+        <v>-9.706999999999999</v>
       </c>
       <c r="T27" t="n">
-        <v>-5.3277</v>
+        <v>-5.327700000000001</v>
       </c>
       <c r="U27" t="n">
-        <v>-4.3795</v>
+        <v>-4.3793</v>
       </c>
       <c r="V27" t="n">
         <v>3.7194</v>
       </c>
       <c r="W27" t="n">
-        <v>6.2103</v>
+        <v>6.210299999999999</v>
       </c>
       <c r="X27" t="n">
         <v>-2.491</v>
